--- a/merged_results_match_filtered.xlsx
+++ b/merged_results_match_filtered.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/xiaojuzhang/Github/pdb_prune/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{52DBA24D-5AE3-C54D-9C84-908063B8ADAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{AD6A3EAF-EE1D-434C-8C3B-1D5B6438D19C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="34560" yWindow="3800" windowWidth="68800" windowHeight="28300" activeTab="3" xr2:uid="{4289B35F-C194-7848-BEAB-2B473BAB1F0C}"/>
+    <workbookView xWindow="4380" yWindow="3060" windowWidth="28040" windowHeight="17100" xr2:uid="{4289B35F-C194-7848-BEAB-2B473BAB1F0C}"/>
   </bookViews>
   <sheets>
     <sheet name="merged_results" sheetId="1" r:id="rId1"/>
@@ -1426,7 +1426,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89BB244E-4BCE-8941-B1CA-0CAB88D90CB0}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:G275"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
@@ -1499,7 +1498,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -1591,7 +1590,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>16</v>
       </c>
@@ -1614,7 +1613,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>17</v>
       </c>
@@ -1706,7 +1705,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>20</v>
       </c>
@@ -1775,7 +1774,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>21</v>
       </c>
@@ -1959,7 +1958,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>30</v>
       </c>
@@ -1982,7 +1981,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>30</v>
       </c>
@@ -2051,8 +2050,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A28" t="s">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A28" s="2" t="s">
         <v>34</v>
       </c>
       <c r="B28" t="s">
@@ -2074,8 +2073,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A29" t="s">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A29" s="2" t="s">
         <v>34</v>
       </c>
       <c r="B29" t="s">
@@ -2097,8 +2096,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A30" t="s">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A30" s="2" t="s">
         <v>34</v>
       </c>
       <c r="B30" t="s">
@@ -2120,8 +2119,8 @@
         <v>9</v>
       </c>
     </row>
-    <row r="31" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A31" t="s">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A31" s="2" t="s">
         <v>34</v>
       </c>
       <c r="B31" t="s">
@@ -2143,8 +2142,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A32" t="s">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A32" s="2" t="s">
         <v>34</v>
       </c>
       <c r="B32" t="s">
@@ -2166,8 +2165,8 @@
         <v>9</v>
       </c>
     </row>
-    <row r="33" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A33" t="s">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A33" s="2" t="s">
         <v>34</v>
       </c>
       <c r="B33" t="s">
@@ -2189,8 +2188,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A34" t="s">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A34" s="2" t="s">
         <v>34</v>
       </c>
       <c r="B34" t="s">
@@ -2212,8 +2211,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A35" t="s">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A35" s="2" t="s">
         <v>34</v>
       </c>
       <c r="B35" t="s">
@@ -2235,8 +2234,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A36" t="s">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A36" s="2" t="s">
         <v>34</v>
       </c>
       <c r="B36" t="s">
@@ -2258,8 +2257,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A37" t="s">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A37" s="2" t="s">
         <v>34</v>
       </c>
       <c r="B37" t="s">
@@ -2281,8 +2280,8 @@
         <v>9</v>
       </c>
     </row>
-    <row r="38" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A38" t="s">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A38" s="2" t="s">
         <v>34</v>
       </c>
       <c r="B38" t="s">
@@ -2304,8 +2303,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A39" t="s">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A39" s="2" t="s">
         <v>34</v>
       </c>
       <c r="B39" t="s">
@@ -2327,8 +2326,8 @@
         <v>9</v>
       </c>
     </row>
-    <row r="40" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A40" t="s">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A40" s="2" t="s">
         <v>34</v>
       </c>
       <c r="B40" t="s">
@@ -2350,8 +2349,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A41" t="s">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A41" s="2" t="s">
         <v>34</v>
       </c>
       <c r="B41" t="s">
@@ -2373,7 +2372,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>47</v>
       </c>
@@ -2396,7 +2395,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>47</v>
       </c>
@@ -2419,7 +2418,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="44" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>47</v>
       </c>
@@ -2442,7 +2441,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>47</v>
       </c>
@@ -2465,7 +2464,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>47</v>
       </c>
@@ -2488,7 +2487,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>47</v>
       </c>
@@ -2511,7 +2510,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="48" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>47</v>
       </c>
@@ -2534,7 +2533,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>47</v>
       </c>
@@ -2557,7 +2556,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>49</v>
       </c>
@@ -2580,7 +2579,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>49</v>
       </c>
@@ -2603,7 +2602,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>49</v>
       </c>
@@ -2649,7 +2648,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="54" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>49</v>
       </c>
@@ -2672,7 +2671,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>49</v>
       </c>
@@ -2695,7 +2694,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>49</v>
       </c>
@@ -2718,7 +2717,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>49</v>
       </c>
@@ -2741,7 +2740,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>49</v>
       </c>
@@ -2764,7 +2763,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>49</v>
       </c>
@@ -2787,7 +2786,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>49</v>
       </c>
@@ -2810,7 +2809,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>49</v>
       </c>
@@ -2833,7 +2832,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>50</v>
       </c>
@@ -2856,7 +2855,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>50</v>
       </c>
@@ -2902,7 +2901,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>50</v>
       </c>
@@ -2925,7 +2924,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>50</v>
       </c>
@@ -2948,7 +2947,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
         <v>51</v>
       </c>
@@ -2971,7 +2970,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
         <v>51</v>
       </c>
@@ -3017,7 +3016,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
         <v>51</v>
       </c>
@@ -3063,7 +3062,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
         <v>52</v>
       </c>
@@ -3086,7 +3085,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
         <v>52</v>
       </c>
@@ -3201,7 +3200,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>55</v>
       </c>
@@ -3224,7 +3223,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
         <v>55</v>
       </c>
@@ -3247,7 +3246,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
         <v>55</v>
       </c>
@@ -3293,7 +3292,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
         <v>60</v>
       </c>
@@ -3362,7 +3361,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="85" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
         <v>62</v>
       </c>
@@ -3385,7 +3384,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
         <v>62</v>
       </c>
@@ -3408,7 +3407,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
         <v>62</v>
       </c>
@@ -3431,7 +3430,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
         <v>62</v>
       </c>
@@ -3454,7 +3453,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
         <v>62</v>
       </c>
@@ -3477,7 +3476,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
         <v>64</v>
       </c>
@@ -3523,7 +3522,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="92" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
         <v>64</v>
       </c>
@@ -3615,7 +3614,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="96" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
         <v>66</v>
       </c>
@@ -3707,7 +3706,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="100" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
         <v>68</v>
       </c>
@@ -3753,7 +3752,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="102" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
         <v>69</v>
       </c>
@@ -3799,7 +3798,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="104" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
         <v>72</v>
       </c>
@@ -3822,7 +3821,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="105" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
         <v>72</v>
       </c>
@@ -3868,7 +3867,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="107" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
         <v>72</v>
       </c>
@@ -3891,7 +3890,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="108" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
         <v>73</v>
       </c>
@@ -3914,7 +3913,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="109" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
         <v>73</v>
       </c>
@@ -3960,7 +3959,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="111" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
         <v>73</v>
       </c>
@@ -3983,7 +3982,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
         <v>73</v>
       </c>
@@ -4006,7 +4005,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
         <v>73</v>
       </c>
@@ -4121,7 +4120,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="118" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
         <v>77</v>
       </c>
@@ -4144,7 +4143,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
         <v>77</v>
       </c>
@@ -4167,7 +4166,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="120" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
         <v>77</v>
       </c>
@@ -4190,7 +4189,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="121" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
         <v>77</v>
       </c>
@@ -4213,7 +4212,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
         <v>80</v>
       </c>
@@ -4236,7 +4235,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
         <v>80</v>
       </c>
@@ -4259,7 +4258,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
         <v>80</v>
       </c>
@@ -4282,7 +4281,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
         <v>80</v>
       </c>
@@ -4305,7 +4304,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
         <v>80</v>
       </c>
@@ -4328,7 +4327,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
         <v>80</v>
       </c>
@@ -4351,7 +4350,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
         <v>80</v>
       </c>
@@ -4374,7 +4373,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="129" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
         <v>80</v>
       </c>
@@ -4397,7 +4396,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="130" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
         <v>80</v>
       </c>
@@ -4420,7 +4419,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="131" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
         <v>80</v>
       </c>
@@ -4443,7 +4442,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="132" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
         <v>80</v>
       </c>
@@ -4466,7 +4465,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="133" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
         <v>80</v>
       </c>
@@ -4489,7 +4488,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="134" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
         <v>80</v>
       </c>
@@ -4512,7 +4511,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="135" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A135" t="s">
         <v>80</v>
       </c>
@@ -4535,7 +4534,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="136" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A136" t="s">
         <v>80</v>
       </c>
@@ -4581,7 +4580,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="138" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A138" t="s">
         <v>80</v>
       </c>
@@ -4604,7 +4603,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="139" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A139" t="s">
         <v>80</v>
       </c>
@@ -4627,7 +4626,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="140" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A140" t="s">
         <v>80</v>
       </c>
@@ -4650,7 +4649,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="141" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A141" t="s">
         <v>80</v>
       </c>
@@ -4673,7 +4672,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="142" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A142" t="s">
         <v>102</v>
       </c>
@@ -4742,7 +4741,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="145" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A145" t="s">
         <v>105</v>
       </c>
@@ -4765,7 +4764,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="146" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A146" t="s">
         <v>105</v>
       </c>
@@ -4926,7 +4925,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="153" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A153" t="s">
         <v>110</v>
       </c>
@@ -4949,7 +4948,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="154" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A154" t="s">
         <v>110</v>
       </c>
@@ -4972,7 +4971,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="155" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A155" t="s">
         <v>111</v>
       </c>
@@ -4995,7 +4994,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="156" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A156" t="s">
         <v>111</v>
       </c>
@@ -5018,7 +5017,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="157" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A157" t="s">
         <v>111</v>
       </c>
@@ -5041,7 +5040,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="158" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A158" t="s">
         <v>111</v>
       </c>
@@ -5087,7 +5086,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="160" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A160" t="s">
         <v>112</v>
       </c>
@@ -5133,7 +5132,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="162" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A162" t="s">
         <v>112</v>
       </c>
@@ -5248,7 +5247,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="167" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A167" t="s">
         <v>118</v>
       </c>
@@ -5271,7 +5270,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="168" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A168" t="s">
         <v>118</v>
       </c>
@@ -5317,7 +5316,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="170" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A170" t="s">
         <v>118</v>
       </c>
@@ -5455,7 +5454,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="176" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A176" t="s">
         <v>123</v>
       </c>
@@ -5478,7 +5477,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="177" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A177" t="s">
         <v>124</v>
       </c>
@@ -5524,7 +5523,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="179" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A179" t="s">
         <v>125</v>
       </c>
@@ -5570,7 +5569,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="181" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A181" t="s">
         <v>125</v>
       </c>
@@ -5593,7 +5592,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="182" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A182" t="s">
         <v>125</v>
       </c>
@@ -5662,7 +5661,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="185" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A185" t="s">
         <v>128</v>
       </c>
@@ -5754,7 +5753,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="189" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A189" t="s">
         <v>133</v>
       </c>
@@ -5892,7 +5891,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="195" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A195" t="s">
         <v>137</v>
       </c>
@@ -5915,7 +5914,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="196" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A196" t="s">
         <v>137</v>
       </c>
@@ -5938,7 +5937,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="197" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A197" t="s">
         <v>137</v>
       </c>
@@ -6053,7 +6052,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="202" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A202" t="s">
         <v>140</v>
       </c>
@@ -6076,7 +6075,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="203" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A203" t="s">
         <v>140</v>
       </c>
@@ -6168,7 +6167,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="207" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A207" t="s">
         <v>142</v>
       </c>
@@ -6191,7 +6190,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="208" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A208" t="s">
         <v>142</v>
       </c>
@@ -6214,7 +6213,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="209" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A209" t="s">
         <v>142</v>
       </c>
@@ -6306,8 +6305,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="213" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A213" t="s">
+    <row r="213" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A213" s="2" t="s">
         <v>147</v>
       </c>
       <c r="B213" t="s">
@@ -6329,8 +6328,8 @@
         <v>9</v>
       </c>
     </row>
-    <row r="214" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A214" t="s">
+    <row r="214" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A214" s="2" t="s">
         <v>147</v>
       </c>
       <c r="B214" t="s">
@@ -6352,8 +6351,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="215" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A215" t="s">
+    <row r="215" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A215" s="2" t="s">
         <v>147</v>
       </c>
       <c r="B215" t="s">
@@ -6375,8 +6374,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="216" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A216" t="s">
+    <row r="216" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A216" s="2" t="s">
         <v>147</v>
       </c>
       <c r="B216" t="s">
@@ -6398,8 +6397,8 @@
         <v>9</v>
       </c>
     </row>
-    <row r="217" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A217" t="s">
+    <row r="217" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A217" s="2" t="s">
         <v>147</v>
       </c>
       <c r="B217" t="s">
@@ -6421,8 +6420,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="218" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A218" t="s">
+    <row r="218" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A218" s="2" t="s">
         <v>147</v>
       </c>
       <c r="B218" t="s">
@@ -6467,7 +6466,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="220" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A220" t="s">
         <v>150</v>
       </c>
@@ -6490,7 +6489,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="221" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A221" t="s">
         <v>150</v>
       </c>
@@ -6513,7 +6512,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="222" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A222" t="s">
         <v>150</v>
       </c>
@@ -6582,7 +6581,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="225" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A225" t="s">
         <v>153</v>
       </c>
@@ -6605,7 +6604,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="226" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A226" t="s">
         <v>153</v>
       </c>
@@ -6651,7 +6650,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="228" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A228" t="s">
         <v>153</v>
       </c>
@@ -6674,7 +6673,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="229" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A229" t="s">
         <v>153</v>
       </c>
@@ -6720,7 +6719,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="231" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A231" t="s">
         <v>155</v>
       </c>
@@ -6743,7 +6742,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="232" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A232" t="s">
         <v>155</v>
       </c>
@@ -6766,7 +6765,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="233" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A233" t="s">
         <v>155</v>
       </c>
@@ -6789,7 +6788,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="234" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A234" t="s">
         <v>155</v>
       </c>
@@ -6812,7 +6811,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="235" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A235" t="s">
         <v>155</v>
       </c>
@@ -6835,7 +6834,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="236" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A236" t="s">
         <v>155</v>
       </c>
@@ -6950,7 +6949,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="241" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A241" t="s">
         <v>159</v>
       </c>
@@ -6973,7 +6972,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="242" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A242" t="s">
         <v>160</v>
       </c>
@@ -6996,7 +6995,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="243" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A243" t="s">
         <v>160</v>
       </c>
@@ -7019,7 +7018,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="244" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A244" t="s">
         <v>160</v>
       </c>
@@ -7042,7 +7041,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="245" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="245" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A245" t="s">
         <v>160</v>
       </c>
@@ -7134,7 +7133,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="249" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="249" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A249" t="s">
         <v>162</v>
       </c>
@@ -7203,7 +7202,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="252" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="252" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A252" t="s">
         <v>164</v>
       </c>
@@ -7249,7 +7248,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="254" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="254" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A254" t="s">
         <v>165</v>
       </c>
@@ -7341,7 +7340,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="258" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="258" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A258" t="s">
         <v>169</v>
       </c>
@@ -7364,7 +7363,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="259" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="259" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A259" t="s">
         <v>169</v>
       </c>
@@ -7387,7 +7386,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="260" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="260" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A260" t="s">
         <v>169</v>
       </c>
@@ -7410,7 +7409,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="261" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="261" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A261" t="s">
         <v>169</v>
       </c>
@@ -7456,7 +7455,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="263" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="263" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A263" t="s">
         <v>169</v>
       </c>
@@ -7479,7 +7478,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="264" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="264" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A264" t="s">
         <v>169</v>
       </c>
@@ -7548,7 +7547,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="267" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="267" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A267" t="s">
         <v>173</v>
       </c>
@@ -7594,7 +7593,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="269" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="269" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A269" t="s">
         <v>173</v>
       </c>
@@ -7617,7 +7616,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="270" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="270" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A270" t="s">
         <v>173</v>
       </c>
@@ -7640,7 +7639,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="271" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="271" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A271" t="s">
         <v>173</v>
       </c>
@@ -7663,7 +7662,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="272" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="272" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A272" t="s">
         <v>173</v>
       </c>
@@ -7686,7 +7685,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="273" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="273" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A273" t="s">
         <v>175</v>
       </c>
@@ -7709,7 +7708,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="274" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="274" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A274" t="s">
         <v>175</v>
       </c>
@@ -7756,14 +7755,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="F1:G275" xr:uid="{89BB244E-4BCE-8941-B1CA-0CAB88D90CB0}">
-    <filterColumn colId="1">
-      <filters>
-        <filter val="1"/>
-        <filter val="2"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="F1:G275" xr:uid="{89BB244E-4BCE-8941-B1CA-0CAB88D90CB0}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
